--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2727-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2727-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2427FCED-8390-4F58-A457-DAE5D064ED28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1219E650-A7C6-44BE-88EB-75C782B25398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{40628976-3FD7-4417-8429-8ECE9DF642DD}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{DF781D33-42F3-4A39-9B11-6080D8A6D115}"/>
   </bookViews>
   <sheets>
     <sheet name="2727-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1526,27 +1526,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41337456-CFEB-412C-BECF-DC82F1879287}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07DEEC90-94E8-4E05-B0F1-F1E2B13B4B37}">
   <dimension ref="A1:X22"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1580,7 +1579,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1616,7 +1615,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1668,7 +1667,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1736,7 +1735,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1808,7 +1807,7 @@
         <v>7.45</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1880,7 +1879,7 @@
         <v>8.19</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1952,7 +1951,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2024,7 +2023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2096,7 +2095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2168,7 +2167,7 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2240,7 +2239,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2312,7 +2311,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2384,7 +2383,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2456,7 +2455,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2528,7 +2527,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41">
         <v>2013</v>
       </c>
@@ -2600,7 +2599,7 @@
         <v>4.62</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="43"/>
       <c r="B17" s="44"/>
       <c r="C17" s="18" t="s">
@@ -2628,7 +2627,7 @@
       <c r="W17" s="50"/>
       <c r="X17" s="46"/>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="51">
         <v>2012</v>
       </c>
@@ -2700,7 +2699,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="53"/>
       <c r="B19" s="54"/>
       <c r="C19" s="20" t="s">
@@ -2728,7 +2727,7 @@
       <c r="W19" s="60"/>
       <c r="X19" s="56"/>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2011</v>
       </c>
@@ -2800,7 +2799,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2010</v>
       </c>
@@ -2872,7 +2871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39" t="s">
         <v>44</v>
       </c>
